--- a/Output/arima_model_interruption1_weekly_output.xlsx
+++ b/Output/arima_model_interruption1_weekly_output.xlsx
@@ -1513,7 +1513,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Food Colour/Flavour and Baking Additivies</t>
+          <t>Food Colour/Flavour and Baking Additives</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Sweet Snacks/Baked Foods</t>
+          <t>Sweet Snacks/Sweet Baked Foods</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4973,7 +4973,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Food Colour/Flavour and Baking Additivies</t>
+          <t>Food Colour/Flavour and Baking Additives</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sweet Snacks/Baked Foods</t>
+          <t>Sweet Snacks/Sweet Baked Foods</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -7597,7 +7597,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Food Colour/Flavour and Baking Additivies</t>
+          <t>Food Colour/Flavour and Baking Additives</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -7632,7 +7632,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Food Colour/Flavour and Baking Additivies</t>
+          <t>Food Colour/Flavour and Baking Additives</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -7667,7 +7667,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Food Colour/Flavour and Baking Additivies</t>
+          <t>Food Colour/Flavour and Baking Additives</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -7702,7 +7702,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Food Colour/Flavour and Baking Additivies</t>
+          <t>Food Colour/Flavour and Baking Additives</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -7737,7 +7737,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Food Colour/Flavour and Baking Additivies</t>
+          <t>Food Colour/Flavour and Baking Additives</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Food Colour/Flavour and Baking Additivies</t>
+          <t>Food Colour/Flavour and Baking Additives</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -9032,7 +9032,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Sweet Snacks/Baked Foods</t>
+          <t>Sweet Snacks/Sweet Baked Foods</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -9067,7 +9067,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Sweet Snacks/Baked Foods</t>
+          <t>Sweet Snacks/Sweet Baked Foods</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -9102,7 +9102,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Sweet Snacks/Baked Foods</t>
+          <t>Sweet Snacks/Sweet Baked Foods</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -12611,7 +12611,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Food Colour/Flavour and Baking Additivies</t>
+          <t>Food Colour/Flavour and Baking Additives</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -12899,7 +12899,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sweet Snacks/Baked Foods</t>
+          <t>Sweet Snacks/Sweet Baked Foods</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
